--- a/clean_data/TransHetSurvivalData.xlsx
+++ b/clean_data/TransHetSurvivalData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larrosm\Documents\MG\Manuscripts\Cd phenotype\Data for Phil\Clean_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ueanorwich-my.sharepoint.com/personal/hpd08ucu_uea_ac_uk/Documents/Manuscripts/cardinal_fitness/clean_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19AC5744-6C73-4331-97F4-F6231C3DD709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{19AC5744-6C73-4331-97F4-F6231C3DD709}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0DE6CF8-5CA7-4BF3-838B-D5DF387355D0}"/>
   <bookViews>
-    <workbookView xWindow="38292" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{53A104EF-7CC2-4706-95E7-0B04E59CA8BB}"/>
+    <workbookView minimized="1" xWindow="11730" yWindow="12840" windowWidth="2400" windowHeight="585" xr2:uid="{53A104EF-7CC2-4706-95E7-0B04E59CA8BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -262,9 +262,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -302,7 +302,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -408,7 +408,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -550,7 +550,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -559,15 +559,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9700725C-853C-4F36-9996-B71732E325A0}">
   <dimension ref="A1:F206"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="7.20703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.41796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.05078125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12.85546875" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -584,7 +583,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
@@ -598,7 +597,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -612,7 +611,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -626,7 +625,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -640,7 +639,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
@@ -654,7 +653,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -668,7 +667,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -682,7 +681,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
@@ -696,7 +695,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>13</v>
       </c>
@@ -710,7 +709,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -718,7 +717,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
@@ -732,7 +731,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -746,7 +745,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -760,7 +759,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -774,7 +773,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
@@ -788,7 +787,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -802,7 +801,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
@@ -816,7 +815,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
@@ -830,7 +829,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
@@ -844,7 +843,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -852,7 +851,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
@@ -866,7 +865,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
@@ -880,7 +879,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>25</v>
       </c>
@@ -894,7 +893,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>26</v>
       </c>
@@ -908,7 +907,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
@@ -922,7 +921,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>28</v>
       </c>
@@ -936,7 +935,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>29</v>
       </c>
@@ -950,7 +949,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>30</v>
       </c>
@@ -964,7 +963,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>31</v>
       </c>
@@ -978,7 +977,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -986,7 +985,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -1000,7 +999,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>33</v>
       </c>
@@ -1014,7 +1013,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>34</v>
       </c>
@@ -1028,7 +1027,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>35</v>
       </c>
@@ -1042,7 +1041,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>36</v>
       </c>
@@ -1056,7 +1055,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>37</v>
       </c>
@@ -1070,7 +1069,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
@@ -1084,7 +1083,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>39</v>
       </c>
@@ -1098,7 +1097,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>40</v>
       </c>
@@ -1112,7 +1111,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -1120,7 +1119,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>41</v>
       </c>
@@ -1134,7 +1133,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>42</v>
       </c>
@@ -1148,7 +1147,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>43</v>
       </c>
@@ -1162,7 +1161,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
@@ -1176,7 +1175,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>45</v>
       </c>
@@ -1190,7 +1189,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>46</v>
       </c>
@@ -1204,7 +1203,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>47</v>
       </c>
@@ -1218,7 +1217,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>48</v>
       </c>
@@ -1232,7 +1231,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>49</v>
       </c>
@@ -1246,7 +1245,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>50</v>
       </c>
@@ -1260,7 +1259,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -1268,7 +1267,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>5</v>
       </c>
@@ -1282,7 +1281,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>6</v>
       </c>
@@ -1296,7 +1295,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>7</v>
       </c>
@@ -1310,7 +1309,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>8</v>
       </c>
@@ -1324,7 +1323,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>9</v>
       </c>
@@ -1338,7 +1337,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>10</v>
       </c>
@@ -1352,7 +1351,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>11</v>
       </c>
@@ -1366,7 +1365,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>12</v>
       </c>
@@ -1380,7 +1379,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>13</v>
       </c>
@@ -1394,7 +1393,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>51</v>
       </c>
@@ -1408,7 +1407,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -1416,7 +1415,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>14</v>
       </c>
@@ -1430,7 +1429,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>15</v>
       </c>
@@ -1444,7 +1443,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>16</v>
       </c>
@@ -1458,7 +1457,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>17</v>
       </c>
@@ -1472,7 +1471,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>18</v>
       </c>
@@ -1486,7 +1485,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>19</v>
       </c>
@@ -1500,7 +1499,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>20</v>
       </c>
@@ -1514,7 +1513,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>21</v>
       </c>
@@ -1528,7 +1527,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>22</v>
       </c>
@@ -1542,7 +1541,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -1550,7 +1549,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>23</v>
       </c>
@@ -1564,7 +1563,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>24</v>
       </c>
@@ -1578,7 +1577,7 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>25</v>
       </c>
@@ -1592,7 +1591,7 @@
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>26</v>
       </c>
@@ -1606,7 +1605,7 @@
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>27</v>
       </c>
@@ -1620,7 +1619,7 @@
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>28</v>
       </c>
@@ -1634,7 +1633,7 @@
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>29</v>
       </c>
@@ -1648,7 +1647,7 @@
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>30</v>
       </c>
@@ -1662,7 +1661,7 @@
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>31</v>
       </c>
@@ -1676,7 +1675,7 @@
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>52</v>
       </c>
@@ -1690,7 +1689,7 @@
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -1698,7 +1697,7 @@
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>32</v>
       </c>
@@ -1712,7 +1711,7 @@
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>33</v>
       </c>
@@ -1726,7 +1725,7 @@
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>34</v>
       </c>
@@ -1740,7 +1739,7 @@
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>35</v>
       </c>
@@ -1754,7 +1753,7 @@
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>36</v>
       </c>
@@ -1768,7 +1767,7 @@
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>37</v>
       </c>
@@ -1782,7 +1781,7 @@
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>38</v>
       </c>
@@ -1796,7 +1795,7 @@
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>39</v>
       </c>
@@ -1810,7 +1809,7 @@
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>40</v>
       </c>
@@ -1824,7 +1823,7 @@
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>53</v>
       </c>
@@ -1838,7 +1837,7 @@
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -1846,7 +1845,7 @@
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>41</v>
       </c>
@@ -1860,7 +1859,7 @@
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>42</v>
       </c>
@@ -1874,7 +1873,7 @@
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>43</v>
       </c>
@@ -1888,7 +1887,7 @@
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>44</v>
       </c>
@@ -1902,7 +1901,7 @@
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>45</v>
       </c>
@@ -1916,7 +1915,7 @@
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>46</v>
       </c>
@@ -1930,7 +1929,7 @@
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>47</v>
       </c>
@@ -1944,7 +1943,7 @@
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -1952,7 +1951,7 @@
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>5</v>
       </c>
@@ -1966,7 +1965,7 @@
       </c>
       <c r="F104" s="3"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>6</v>
       </c>
@@ -1980,7 +1979,7 @@
       </c>
       <c r="F105" s="3"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>7</v>
       </c>
@@ -1994,7 +1993,7 @@
       </c>
       <c r="F106" s="3"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>8</v>
       </c>
@@ -2008,7 +2007,7 @@
       </c>
       <c r="F107" s="3"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>9</v>
       </c>
@@ -2022,7 +2021,7 @@
       </c>
       <c r="F108" s="3"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>10</v>
       </c>
@@ -2036,7 +2035,7 @@
       </c>
       <c r="F109" s="3"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>11</v>
       </c>
@@ -2050,7 +2049,7 @@
       </c>
       <c r="F110" s="3"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>12</v>
       </c>
@@ -2064,7 +2063,7 @@
       </c>
       <c r="F111" s="3"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>13</v>
       </c>
@@ -2078,7 +2077,7 @@
       </c>
       <c r="F112" s="3"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>51</v>
       </c>
@@ -2092,7 +2091,7 @@
       </c>
       <c r="F113" s="3"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -2100,7 +2099,7 @@
       <c r="E114" s="3"/>
       <c r="F114" s="3"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>14</v>
       </c>
@@ -2114,7 +2113,7 @@
       </c>
       <c r="F115" s="3"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>15</v>
       </c>
@@ -2128,7 +2127,7 @@
       </c>
       <c r="F116" s="3"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>16</v>
       </c>
@@ -2142,7 +2141,7 @@
       </c>
       <c r="F117" s="3"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>17</v>
       </c>
@@ -2156,7 +2155,7 @@
       </c>
       <c r="F118" s="3"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>18</v>
       </c>
@@ -2170,7 +2169,7 @@
       </c>
       <c r="F119" s="3"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>19</v>
       </c>
@@ -2184,7 +2183,7 @@
       </c>
       <c r="F120" s="3"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>20</v>
       </c>
@@ -2198,7 +2197,7 @@
       </c>
       <c r="F121" s="3"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>21</v>
       </c>
@@ -2212,7 +2211,7 @@
       </c>
       <c r="F122" s="3"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>22</v>
       </c>
@@ -2226,7 +2225,7 @@
       </c>
       <c r="F123" s="3"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -2234,7 +2233,7 @@
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>23</v>
       </c>
@@ -2248,7 +2247,7 @@
       </c>
       <c r="F125" s="3"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>24</v>
       </c>
@@ -2262,7 +2261,7 @@
       </c>
       <c r="F126" s="3"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>25</v>
       </c>
@@ -2276,7 +2275,7 @@
       </c>
       <c r="F127" s="3"/>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>26</v>
       </c>
@@ -2290,7 +2289,7 @@
       </c>
       <c r="F128" s="3"/>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>27</v>
       </c>
@@ -2304,7 +2303,7 @@
       </c>
       <c r="F129" s="3"/>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>28</v>
       </c>
@@ -2318,7 +2317,7 @@
       </c>
       <c r="F130" s="3"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>29</v>
       </c>
@@ -2332,7 +2331,7 @@
       </c>
       <c r="F131" s="3"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>30</v>
       </c>
@@ -2346,7 +2345,7 @@
       </c>
       <c r="F132" s="3"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>31</v>
       </c>
@@ -2360,7 +2359,7 @@
       </c>
       <c r="F133" s="3"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -2368,7 +2367,7 @@
       <c r="E134" s="3"/>
       <c r="F134" s="3"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>32</v>
       </c>
@@ -2382,7 +2381,7 @@
       </c>
       <c r="F135" s="3"/>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>33</v>
       </c>
@@ -2396,7 +2395,7 @@
       </c>
       <c r="F136" s="3"/>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>34</v>
       </c>
@@ -2410,7 +2409,7 @@
       </c>
       <c r="F137" s="3"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>35</v>
       </c>
@@ -2424,7 +2423,7 @@
       </c>
       <c r="F138" s="3"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>36</v>
       </c>
@@ -2438,7 +2437,7 @@
       </c>
       <c r="F139" s="3"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>37</v>
       </c>
@@ -2452,7 +2451,7 @@
       </c>
       <c r="F140" s="3"/>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>38</v>
       </c>
@@ -2466,7 +2465,7 @@
       </c>
       <c r="F141" s="3"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>39</v>
       </c>
@@ -2480,7 +2479,7 @@
       </c>
       <c r="F142" s="3"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>40</v>
       </c>
@@ -2494,7 +2493,7 @@
       </c>
       <c r="F143" s="3"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>53</v>
       </c>
@@ -2508,7 +2507,7 @@
       </c>
       <c r="F144" s="3"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -2516,7 +2515,7 @@
       <c r="E145" s="3"/>
       <c r="F145" s="3"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>41</v>
       </c>
@@ -2530,7 +2529,7 @@
       </c>
       <c r="F146" s="3"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>42</v>
       </c>
@@ -2544,7 +2543,7 @@
       </c>
       <c r="F147" s="3"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>43</v>
       </c>
@@ -2558,7 +2557,7 @@
       </c>
       <c r="F148" s="3"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>44</v>
       </c>
@@ -2572,7 +2571,7 @@
       </c>
       <c r="F149" s="3"/>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>45</v>
       </c>
@@ -2586,7 +2585,7 @@
       </c>
       <c r="F150" s="3"/>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>46</v>
       </c>
@@ -2600,7 +2599,7 @@
       </c>
       <c r="F151" s="3"/>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>47</v>
       </c>
@@ -2614,7 +2613,7 @@
       </c>
       <c r="F152" s="3"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>48</v>
       </c>
@@ -2628,7 +2627,7 @@
       </c>
       <c r="F153" s="3"/>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>49</v>
       </c>
@@ -2642,7 +2641,7 @@
       </c>
       <c r="F154" s="3"/>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>50</v>
       </c>
@@ -2656,7 +2655,7 @@
       </c>
       <c r="F155" s="3"/>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -2664,7 +2663,7 @@
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>5</v>
       </c>
@@ -2678,7 +2677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>6</v>
       </c>
@@ -2692,7 +2691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>7</v>
       </c>
@@ -2706,7 +2705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>8</v>
       </c>
@@ -2720,7 +2719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>9</v>
       </c>
@@ -2734,7 +2733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>10</v>
       </c>
@@ -2748,7 +2747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>11</v>
       </c>
@@ -2762,7 +2761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>12</v>
       </c>
@@ -2776,7 +2775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>13</v>
       </c>
@@ -2790,7 +2789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>51</v>
       </c>
@@ -2804,7 +2803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -2812,7 +2811,7 @@
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>14</v>
       </c>
@@ -2826,7 +2825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>15</v>
       </c>
@@ -2840,7 +2839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>16</v>
       </c>
@@ -2854,7 +2853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>17</v>
       </c>
@@ -2868,7 +2867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>18</v>
       </c>
@@ -2882,7 +2881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>19</v>
       </c>
@@ -2896,7 +2895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>20</v>
       </c>
@@ -2910,7 +2909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>21</v>
       </c>
@@ -2924,7 +2923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -2932,7 +2931,7 @@
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>23</v>
       </c>
@@ -2946,7 +2945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>24</v>
       </c>
@@ -2960,7 +2959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>25</v>
       </c>
@@ -2974,7 +2973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>26</v>
       </c>
@@ -2988,7 +2987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>27</v>
       </c>
@@ -3002,7 +3001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>28</v>
       </c>
@@ -3016,7 +3015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>29</v>
       </c>
@@ -3030,7 +3029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>30</v>
       </c>
@@ -3044,7 +3043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>31</v>
       </c>
@@ -3058,7 +3057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -3066,7 +3065,7 @@
       <c r="E186" s="3"/>
       <c r="F186" s="3"/>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>32</v>
       </c>
@@ -3080,7 +3079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>33</v>
       </c>
@@ -3094,7 +3093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>34</v>
       </c>
@@ -3108,7 +3107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>35</v>
       </c>
@@ -3122,7 +3121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>36</v>
       </c>
@@ -3136,7 +3135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>37</v>
       </c>
@@ -3150,7 +3149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>38</v>
       </c>
@@ -3164,7 +3163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>39</v>
       </c>
@@ -3178,7 +3177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>40</v>
       </c>
@@ -3192,7 +3191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -3200,7 +3199,7 @@
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>41</v>
       </c>
@@ -3214,7 +3213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>42</v>
       </c>
@@ -3228,7 +3227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>43</v>
       </c>
@@ -3242,7 +3241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>44</v>
       </c>
@@ -3256,7 +3255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>45</v>
       </c>
@@ -3270,7 +3269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>46</v>
       </c>
@@ -3284,7 +3283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>47</v>
       </c>
@@ -3298,7 +3297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>48</v>
       </c>
@@ -3312,7 +3311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>49</v>
       </c>
@@ -3326,7 +3325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>50</v>
       </c>
